--- a/Trắc nghiệm ôn luyện/Embedded Hardware/multiple_choice_sample_template_MCU_PERIPHERALS.xlsx
+++ b/Trắc nghiệm ôn luyện/Embedded Hardware/multiple_choice_sample_template_MCU_PERIPHERALS.xlsx
@@ -453,19 +453,19 @@
         <v>UART là giao thức bất đồng bộ (Asynchronous), truyền nhận full-duplex qua 2 đường độc lập Tx và Rx (cần nối chung chân GND làm mốc điện áp).</v>
       </c>
       <c r="E2" t="str">
+        <v>4 dây tín hiệu: MISO, MOSI, SCK, và SS — phục vụ truyền nhận dữ liệu đồng bộ</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1 dây tín hiệu duy nhất dùng chung cho cả truyền và nhận dữ liệu đồng thời</v>
+      </c>
+      <c r="G2" t="str">
         <v>2 dây tín hiệu: Tx (Truyền) và Rx (Nhận) — kết nối chéo giữa hai thiết bị (Tx thiết bị A nối Rx thiết bị B)</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>3 dây tín hiệu: SCL (Xung nhịp), SDA (Dữ liệu), và GND (Đất)</v>
       </c>
-      <c r="G2" t="str">
-        <v>4 dây tín hiệu: MISO, MOSI, SCK, và SS — phục vụ truyền nhận dữ liệu đồng bộ</v>
-      </c>
-      <c r="H2" t="str">
-        <v>1 dây tín hiệu duy nhất dùng chung cho cả truyền và nhận dữ liệu đồng thời</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Do không có đường truyền xung nhịp (Clock) để đồng bộ cứng, UART sử dụng Baudrate thiết lập sẵn và các bit Start/Stop trong khung truyền để đồng bộ luồng nhận.</v>
       </c>
       <c r="E3" t="str">
+        <v>Vì nó chỉ cho phép truyền dữ liệu theo một chiều duy nhất tại một thời điểm</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Vì tín hiệu truyền đi không cần tuân theo bất kỳ định dạng khung truyền nào</v>
+      </c>
+      <c r="G3" t="str">
         <v>Vì nó không sử dụng dây dẫn tín hiệu xung nhịp (Clock) chung giữa hai thiết bị; hai bên tự thống nhất tốc độ truyền (Baud rate)</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>Vì tốc độ truyền dữ liệu của nó thay đổi liên tục một cách ngẫu nhiên khi chạy</v>
       </c>
-      <c r="G3" t="str">
-        <v>Vì nó chỉ cho phép truyền dữ liệu theo một chiều duy nhất tại một thời điểm</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Vì tín hiệu truyền đi không cần tuân theo bất kỳ định dạng khung truyền nào</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>I2C là giao thức đồng bộ (Synchronous), half-duplex, sử dụng đường dữ liệu SDA và đường xung nhịp SCL để điều phối việc truyền tin.</v>
       </c>
       <c r="E4" t="str">
-        <v>SDA (Serial Data) dùng để truyền nhận dữ liệu; SCL (Serial Clock) dùng để truyền tín hiệu xung nhịp đồng bộ</v>
+        <v>SDA dùng để truyền tín hiệu bắt đầu; SCL dùng để truyền tín hiệu kết thúc giao tiếp</v>
       </c>
       <c r="F4" t="str">
         <v>SDA dùng để cấp nguồn điện; SCL dùng để nối đất cho mạch ngoại vi</v>
       </c>
       <c r="G4" t="str">
-        <v>SDA dùng để truyền tín hiệu bắt đầu; SCL dùng để truyền tín hiệu kết thúc giao tiếp</v>
+        <v>Cả hai dây SDA và SCL đều thực hiện truyền nhận dữ liệu song song để tăng tốc độ</v>
       </c>
       <c r="H4" t="str">
-        <v>Cả hai dây SDA và SCL đều thực hiện truyền nhận dữ liệu song song để tăng tốc độ</v>
+        <v>SDA (Serial Data) dùng để truyền nhận dữ liệu; SCL (Serial Clock) dùng để truyền tín hiệu xung nhịp đồng bộ</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -546,10 +546,10 @@
         <v>SCK (Serial Clock) — dùng để phát xung nhịp đồng bộ từ Master</v>
       </c>
       <c r="G5" t="str">
+        <v>MISO (Master In Slave Out) — dùng để nhận dữ liệu từ Slave về Master</v>
+      </c>
+      <c r="H5" t="str">
         <v>MOSI (Master Out Slave In) — dùng để truyền dữ liệu từ Master đến Slave</v>
-      </c>
-      <c r="H5" t="str">
-        <v>MISO (Master In Slave Out) — dùng để nhận dữ liệu từ Slave về Master</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -569,19 +569,19 @@
         <v>Chân GPIO để trống ở chế độ Input sẽ bị nhiễu môi trường làm thay đổi logic liên tục (floating). Pull-up kéo chân lên mức VCC để đảm bảo trạng thái logic ổn định.</v>
       </c>
       <c r="E6" t="str">
-        <v>Giữ chân GPIO luôn ở mức điện áp cao (Logic 1) khi không có tín hiệu bên ngoài tác động, tránh trạng thái lơ lửng (Floating)</v>
+        <v>Tự động chuyển đổi chân GPIO từ chế độ đầu vào sang chế độ đầu ra</v>
       </c>
       <c r="F6" t="str">
         <v>Tăng dòng điện đầu ra tối đa của chân GPIO để thắp sáng các bóng đèn công suất lớn</v>
       </c>
       <c r="G6" t="str">
+        <v>Giữ chân GPIO luôn ở mức điện áp cao (Logic 1) khi không có tín hiệu bên ngoài tác động, tránh trạng thái lơ lửng (Floating)</v>
+      </c>
+      <c r="H6" t="str">
         <v>Bảo vệ vi điều khiển chống lại các hiện tượng quá áp hoặc sét đánh vào mạch</v>
       </c>
-      <c r="H6" t="str">
-        <v>Tự động chuyển đổi chân GPIO từ chế độ đầu vào sang chế độ đầu ra</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -601,13 +601,13 @@
         <v>Chuyển đổi tín hiệu điện áp liên tục (Analog) bên ngoài thành giá trị số (Digital) để CPU xử lý</v>
       </c>
       <c r="F7" t="str">
+        <v>Chuyển đổi dòng điện xoay chiều (AC) thành dòng điện một chiều (DC) cấp nguồn cho mạch</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Tăng tần số xung nhịp hoạt động của nhân vi điều khiển lên tối đa</v>
+      </c>
+      <c r="H7" t="str">
         <v>Chuyển đổi các câu lệnh lập trình C thành mã máy nhị phân nạp vào Flash</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Chuyển đổi dòng điện xoay chiều (AC) thành dòng điện một chiều (DC) cấp nguồn cho mạch</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Tăng tần số xung nhịp hoạt động của nhân vi điều khiển lên tối đa</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -630,10 +630,10 @@
         <v>Cho phép truyền dữ liệu trực tiếp giữa bộ nhớ và ngoại vi (hoặc bộ nhớ - bộ nhớ) mà không cần sự can thiệp của CPU, giúp giải phóng tài nguyên CPU</v>
       </c>
       <c r="F8" t="str">
+        <v>Cho phép vi điều khiển kết nối trực tiếp vào mạng internet không dây Wi-Fi</v>
+      </c>
+      <c r="G8" t="str">
         <v>Tự động tối ưu hóa cấu trúc của các bảng cơ sở dữ liệu quan hệ lưu trữ trên vi điều khiển</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Cho phép vi điều khiển kết nối trực tiếp vào mạng internet không dây Wi-Fi</v>
       </c>
       <c r="H8" t="str">
         <v>Tự động tăng gấp đôi dung lượng bộ nhớ RAM vật lý của hệ thống vi điều khiển</v>
@@ -656,19 +656,19 @@
         <v>SPI sử dụng 2 đường dữ liệu riêng biệt MOSI và MISO hoạt động đồng bộ theo nhịp SCK, cho phép gửi và nhận dữ liệu đồng thời ở tốc độ rất cao.</v>
       </c>
       <c r="E9" t="str">
-        <v>Full-duplex (Song công) — cho phép truyền và nhận dữ liệu đồng thời trên hai đường MOSI và MISO độc lập</v>
+        <v>Simplex (Đơn công) — chỉ cho phép truyền dữ liệu một chiều cố định từ Master đến Slave</v>
       </c>
       <c r="F9" t="str">
         <v>Half-duplex (Bán song công) — chỉ cho phép truyền hoặc nhận tại một thời điểm trên một dây dẫn</v>
       </c>
       <c r="G9" t="str">
-        <v>Simplex (Đơn công) — chỉ cho phép truyền dữ liệu một chiều cố định từ Master đến Slave</v>
+        <v>Asynchronous (Bất đồng bộ) — truyền dữ liệu không cần đồng bộ xung nhịp</v>
       </c>
       <c r="H9" t="str">
-        <v>Asynchronous (Bất đồng bộ) — truyền dữ liệu không cần đồng bộ xung nhịp</v>
+        <v>Full-duplex (Song công) — cho phép truyền và nhận dữ liệu đồng thời trên hai đường MOSI và MISO độc lập</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Cấu trúc Open-drain chỉ có khả năng kéo bus xuống 0. Khi không ai truyền, bus được đưa về mức 1 nhờ điện trở kéo lên. Thiết kế này tránh ngắn mạch khi nhiều thiết bị cùng truyền tin.</v>
       </c>
       <c r="E10" t="str">
+        <v>Để cách ly điện áp giữa thiết bị Master và các thiết bị Slave trên cùng một bus</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Để chuyển đổi tín hiệu từ dạng tương tự (Analog) sang dạng số (Digital) một cách tự động</v>
+      </c>
+      <c r="G10" t="str">
         <v>Vì các chân I2C của thiết bị được thiết kế theo cấu trúc Cực thu hở (Open-drain / Open-collector); điện trở kéo lên giúp kéo đường truyền lên mức cao khi các thiết bị không kéo xuống mức thấp</v>
       </c>
-      <c r="F10" t="str">
+      <c r="H10" t="str">
         <v>Để hạn chế dòng điện chạy qua các thiết bị tránh gây cháy chip khi truyền tin ở tốc độ cao</v>
       </c>
-      <c r="G10" t="str">
-        <v>Để chuyển đổi tín hiệu từ dạng tương tự (Analog) sang dạng số (Digital) một cách tự động</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Để cách ly điện áp giữa thiết bị Master và các thiết bị Slave trên cùng một bus</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Tổ hợp CPOL và CPHA tạo ra 4 chế độ chạy của SPI (Mode 0, 1, 2, 3), đảm bảo Master và Slave lấy mẫu (sampling) và dịch bit (shifting) tại đúng thời điểm sườn xung nhịp.</v>
       </c>
       <c r="E11" t="str">
+        <v>CPOL điều khiển điện áp sườn xung; CPHA điều khiển độ trễ thời gian phản hồi</v>
+      </c>
+      <c r="F11" t="str">
         <v>CPOL xác định trạng thái của đường Clock khi không truyền tin (Idle); CPHA xác định sườn xung nhịp (cạnh lên hay cạnh xuống) dùng để lấy mẫu dữ liệu</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>CPOL xác định tốc độ Baudrate tối đa; CPHA xác định số bit dữ liệu trong một khung truyền</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>CPOL cấu hình chế độ Master; CPHA cấu hình chế độ Slave của thiết bị</v>
       </c>
-      <c r="H11" t="str">
-        <v>CPOL điều khiển điện áp sườn xung; CPHA điều khiển độ trễ thời gian phản hồi</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>I2C sử dụng cơ chế định địa chỉ phần mềm (thường là 7-bit hoặc 10-bit). Slave chỉ nhận và phản hồi gói tin khi byte địa chỉ Master gửi đi trùng khớp với địa chỉ của mình.</v>
       </c>
       <c r="E12" t="str">
+        <v>Sử dụng các dây chọn chip SS/CS riêng biệt nối từ Master đến từng Slave</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Các Slave tự động phân xử dựa trên mức điện áp sườn xung nhịp SCL</v>
+      </c>
+      <c r="G12" t="str">
         <v>Sử dụng địa chỉ định danh (Address) duy nhất của từng Slave; Master gửi địa chỉ này lên bus trước khi truyền dữ liệu để chỉ định Slave phản hồi</v>
       </c>
-      <c r="F12" t="str">
-        <v>Sử dụng các dây chọn chip SS/CS riêng biệt nối từ Master đến từng Slave</v>
-      </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Sử dụng cơ chế phân chia thời gian truyền tin (TDMA) một cách tự động</v>
       </c>
-      <c r="H12" t="str">
-        <v>Các Slave tự động phân xử dựa trên mức điện áp sườn xung nhịp SCL</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -772,19 +772,19 @@
         <v>Rung phím (bounce) xảy ra trong vài ms khi nhấn nút. Dùng delay trong ISR là cấm kỵ. Giải pháp tốt nhất là nhận ngắt, tắt ngắt tạm thời, bật timer 20ms sau quét lại trạng thái nút và bật lại ngắt.</v>
       </c>
       <c r="E13" t="str">
-        <v>Sử dụng ngắt cạnh (Edge Interrupt) kết hợp với bộ định thời (Timer) để trì hoãn việc đọc lại trạng thái phím sau khoảng 10-20ms (chống nhiễu rung cơ học)</v>
+        <v>Thực hiện vòng lặp vô hạn kiểm tra liên tục trạng thái nút bấm trong luồng chương trình chính</v>
       </c>
       <c r="F13" t="str">
         <v>Sử dụng hàm `delay_ms(20)` trực tiếp bên trong hàm phục vụ ngắt ISR của nút bấm</v>
       </c>
       <c r="G13" t="str">
-        <v>Thực hiện vòng lặp vô hạn kiểm tra liên tục trạng thái nút bấm trong luồng chương trình chính</v>
+        <v>Lắp đặt thêm tụ điện phân cực dung lượng lớn song song với tiếp điểm nút bấm</v>
       </c>
       <c r="H13" t="str">
-        <v>Lắp đặt thêm tụ điện phân cực dung lượng lớn song song với tiếp điểm nút bấm</v>
+        <v>Sử dụng ngắt cạnh (Edge Interrupt) kết hợp với bộ định thời (Timer) để trì hoãn việc đọc lại trạng thái phím sau khoảng 10-20ms (chống nhiễu rung cơ học)</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -801,10 +801,10 @@
         <v>Bit Parity là phương pháp kiểm tra lỗi đơn giản. Even parity đảm bảo tổng số bit 1 trong frame là chẵn. Nếu nhận được số bit 1 không khớp, hệ thống phát hiện lỗi và hủy gói.</v>
       </c>
       <c r="E14" t="str">
+        <v>Tăng tốc độ truyền nhận dữ liệu của khung truyền lên gấp đôi</v>
+      </c>
+      <c r="F14" t="str">
         <v>Kiểm tra lỗi truyền dẫn cơ bản bằng cách đếm số lượng bit 1 trong khung truyền để phát hiện việc bị đảo bit ngẫu nhiên</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Tăng tốc độ truyền nhận dữ liệu của khung truyền lên gấp đôi</v>
       </c>
       <c r="G14" t="str">
         <v>Định nghĩa điểm bắt đầu và kết thúc của một khung truyền dữ liệu nối tiếp</v>
@@ -813,7 +813,7 @@
         <v>Đóng vai trò làm mật mã khóa để xác thực danh tính thiết bị gửi tin</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Chế độ Open-drain hữu ích khi cần giao tiếp giữa các IC chạy mức điện áp khác nhau (ví dụ: MCU 3.3V giao tiếp IC 5V bằng cách kéo điện trở lên 5V) hoặc chạy bus nhiều Master/Slave như I2C.</v>
       </c>
       <c r="E15" t="str">
+        <v>Chân chỉ cho phép truyền dữ liệu một chiều ra ngoài và không thể đọc lại trạng thái</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Chân tự động hoạt động như một chân đầu vào Analog để đọc điện áp cảm biến</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Chân có thể tự động đẩy dòng điện lên mức điện áp tối đa mà không cần nguồn cấp ngoài</v>
+      </c>
+      <c r="H15" t="str">
         <v>Chỉ có khả năng kéo chân xuống mức 0 (GND); khi xuất mức 1, chân ở trạng thái trở kháng cao (Hi-Z) và cần điện trở kéo lên để đạt mức VCC</v>
       </c>
-      <c r="F15" t="str">
-        <v>Chân có thể tự động đẩy dòng điện lên mức điện áp tối đa mà không cần nguồn cấp ngoài</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Chân tự động hoạt động như một chân đầu vào Analog để đọc điện áp cảm biến</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Chân chỉ cho phép truyền dữ liệu một chiều ra ngoài và không thể đọc lại trạng thái</v>
-      </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>Input Capture chụp (capture) lại giá trị đếm của Timer khi có ngắt sườn lên/xuống ở chân tín hiệu, giúp tính toán chính xác khoảng thời gian giữa hai sườn (đo tần số/độ rộng xung).</v>
       </c>
       <c r="E16" t="str">
-        <v>Đo đạc chu kỳ, tần số hoặc độ rộng xung của một tín hiệu đầu vào bằng cách ghi lại giá trị counter tại thời điểm xảy ra sườn xung kích hoạt</v>
+        <v>Tự động sao lưu dữ liệu từ bộ nhớ Flash sang bộ nhớ RAM của vi điều khiển</v>
       </c>
       <c r="F16" t="str">
         <v>Tạo ra các xung PWM có chu kỳ và độ rộng xung thay đổi liên tục để điều khiển động cơ</v>
       </c>
       <c r="G16" t="str">
-        <v>Tự động sao lưu dữ liệu từ bộ nhớ Flash sang bộ nhớ RAM của vi điều khiển</v>
+        <v>Đo đạc chu kỳ, tần số hoặc độ rộng xung của một tín hiệu đầu vào bằng cách ghi lại giá trị counter tại thời điểm xảy ra sườn xung kích hoạt</v>
       </c>
       <c r="H16" t="str">
         <v>Đếm số lượng câu lệnh mã máy chạy được trong một khoảng thời gian</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>I2C tiết kiệm chân phần cứng (chỉ cần 2 chân cho bus nhiều thiết bị). SPI tốn chân hơn vì mỗi thiết bị Slave cần một đường CS riêng biệt nối từ Master (hoặc mắc nối tiếp dạng daisy chain).</v>
       </c>
       <c r="E17" t="str">
+        <v>SPI sử dụng điện trở kéo lên trên tất cả các dây; I2C sử dụng kết nối đẩy kéo trực tiếp</v>
+      </c>
+      <c r="F17" t="str">
+        <v>SPI truyền dữ liệu bất đồng bộ; I2C truyền dữ liệu đồng bộ xung nhịp phần cứng</v>
+      </c>
+      <c r="G17" t="str">
+        <v>SPI chỉ hỗ trợ kết nối 1 Master và 1 Slave; I2C hỗ trợ kết nối hàng ngàn Master và Slave cùng lúc</v>
+      </c>
+      <c r="H17" t="str">
         <v>SPI cần tối thiểu 4 dây (MOSI, MISO, SCK, CS); I2C chỉ cần 2 dây (SDA, SCL) bất kể số lượng thiết bị kết nối</v>
       </c>
-      <c r="F17" t="str">
-        <v>SPI chỉ hỗ trợ kết nối 1 Master và 1 Slave; I2C hỗ trợ kết nối hàng ngàn Master và Slave cùng lúc</v>
-      </c>
-      <c r="G17" t="str">
-        <v>SPI sử dụng điện trở kéo lên trên tất cả các dây; I2C sử dụng kết nối đẩy kéo trực tiếp</v>
-      </c>
-      <c r="H17" t="str">
-        <v>SPI truyền dữ liệu bất đồng bộ; I2C truyền dữ liệu đồng bộ xung nhịp phần cứng</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Ví dụ với ADC 12-bit, nếu VREF = 3.3V, giá trị 4095 tương đương 3.3V. Nếu VREF bị sụt áp xuống 3.0V do nguồn yếu, kết quả tính toán điện áp sẽ bị sai lệch hoàn toàn.</v>
       </c>
       <c r="E18" t="str">
-        <v>VREF xác định dải điện áp đầu vào tối đa mà ADC có thể đo được; giá trị số trả về sẽ tỷ lệ thuận giữa điện áp ngõ vào và VREF</v>
+        <v>VREF tự động lọc các nhiễu tần số cao của tín hiệu analog đầu vào</v>
       </c>
       <c r="F18" t="str">
         <v>VREF quyết định tốc độ lấy mẫu tối đa của ADC tính bằng số mẫu trên giây</v>
       </c>
       <c r="G18" t="str">
+        <v>VREF xác định dải điện áp đầu vào tối đa mà ADC có thể đo được; giá trị số trả về sẽ tỷ lệ thuận giữa điện áp ngõ vào và VREF</v>
+      </c>
+      <c r="H18" t="str">
         <v>VREF cung cấp nguồn điện năng chính để nuôi hoạt động của nhân CPU vi điều khiển</v>
       </c>
-      <c r="H18" t="str">
-        <v>VREF tự động lọc các nhiễu tần số cao của tín hiệu analog đầu vào</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -949,13 +949,13 @@
         <v>Sử dụng mức logic trội (Dominant - 0) đè mức logic lặn (Recessive - 1); nút nào có ID nhỏ hơn (nhiều bit 0 hơn ở đầu) sẽ giành được quyền ưu tiên truyền tiếp</v>
       </c>
       <c r="F19" t="str">
+        <v>Bộ điều khiển trung tâm (Master) của mạng CAN sẽ phân chia khe thời gian truyền cho từng nút</v>
+      </c>
+      <c r="G19" t="str">
         <v>Nút nào gửi yêu cầu lên bus trước sẽ giành quyền truyền; nút còn lại sẽ bị ngắt kết nối vật lý khỏi mạng</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Hai nút tự động chia đôi băng thông đường truyền để gửi dữ liệu song song đồng thời</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Bộ điều khiển trung tâm (Master) của mạng CAN sẽ phân chia khe thời gian truyền cho từng nút</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -975,19 +975,19 @@
         <v>Dây dài có điện dung ký sinh lớn tạo thành mạch lọc RC thông thấp làm méo xung nhịp SCL. Giảm điện trở kéo lên (ví dụ từ 10k xuống 2.2k) giúp rút ngắn hằng số thời gian RC, sườn lên dốc hơn, khôi phục dạng sóng xung.</v>
       </c>
       <c r="E20" t="str">
+        <v>Thay thế vi điều khiển bằng một chip có công suất tiêu thụ điện lớn hơn</v>
+      </c>
+      <c r="F20" t="str">
         <v>Giảm trị số điện trở kéo lên (Pull-up Resistors) trên đường SDA/SCL để tăng dòng sạc tụ ký sinh, hoặc giảm tốc độ truyền (I2C Clock Speed)</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>Tăng tần số hoạt động của I2C lên chế độ Fast Mode (400kHz) hoặc High Speed Mode</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Thay thế vi điều khiển bằng một chip có công suất tiêu thụ điện lớn hơn</v>
       </c>
       <c r="H20" t="str">
         <v>Sử dụng bộ biến đổi điện áp để nâng mức logic của I2C từ 3.3V lên 12V trên đường truyền</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Nếu dùng CPU đọc thủ công (polling hoặc ISR), ở tần số lấy mẫu cao (ví dụ 100kHz), CPU sẽ bị ngập trong ngắt, không còn thời gian xử lý việc khác. Timer trigger cứng loại bỏ sai số thời gian (jitter) do độ trễ ngắt phần mềm.</v>
       </c>
       <c r="E21" t="str">
+        <v>Để tăng độ phân giải của ADC từ 12-bit lên thành 24-bit một cách tự động bằng phần cứng</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Vì DMA hỗ trợ tự động lọc các nhiễu tần số cao của tín hiệu điện áp analog</v>
+      </c>
+      <c r="G21" t="str">
         <v>Để đảm bảo chu kỳ lấy mẫu cực kỳ chính xác (jitter thấp) nhờ timer trigger phần cứng, và DMA tự chuyển kết quả vào RAM giúp tránh quá tải ngắt cho CPU ở tần số lấy mẫu cao</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Để tăng độ phân giải của ADC từ 12-bit lên thành 24-bit một cách tự động bằng phần cứng</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Vì DMA hỗ trợ tự động lọc các nhiễu tần số cao của tín hiệu điện áp analog</v>
       </c>
       <c r="H21" t="str">
         <v>Vì CPU của vi điều khiển không hỗ trợ việc đọc dữ liệu ADC trực tiếp bằng lệnh lập trình C</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>ORE xảy ra khi phần mềm xử lý quá chậm. Khi cờ ORE bị set, bộ nhận UART thường bị khóa không nhận thêm dữ liệu. Driver cần phát hiện cờ ORE, đọc thanh ghi status rồi đọc DR để clear cờ lỗi, giải phóng bộ nhận.</v>
       </c>
       <c r="E22" t="str">
+        <v>Khi điện áp cấp trên dây truyền nhận Rx vượt quá giới hạn an toàn 5V của vi điều khiển</v>
+      </c>
+      <c r="F22" t="str">
         <v>Khi một byte dữ liệu mới nhận được ghi đè vào thanh ghi nhận (Receive Data Register) trước khi CPU kịp đọc byte cũ ra; Xử lý: Đọc thanh ghi trạng thái để xóa cờ lỗi ORE và xóa bộ đệm nhận</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
+        <v>Khi khung truyền bị thiếu mất bit Start ở đầu gói dữ liệu nối tiếp</v>
+      </c>
+      <c r="H22" t="str">
         <v>Khi tốc độ Baudrate của thiết bị gửi lớn gấp đôi so với thiết bị nhận dữ liệu</v>
       </c>
-      <c r="G22" t="str">
-        <v>Khi điện áp cấp trên dây truyền nhận Rx vượt quá giới hạn an toàn 5V của vi điều khiển</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Khi khung truyền bị thiếu mất bit Start ở đầu gói dữ liệu nối tiếp</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Hầu hết MCU hiện đại (như ARM, AVR) dùng Memory-mapped I/O, giúp lập trình viên viết code điều khiển thanh ghi bằng con trỏ C rất tự nhiên, tận dụng được tất cả các chế độ định địa chỉ của tập lệnh CPU.</v>
       </c>
       <c r="E23" t="str">
-        <v>Memory-mapped I/O ánh xạ thanh ghi ngoại vi vào không gian địa chỉ bộ nhớ chung, cho phép dùng mọi lệnh truy cập bộ nhớ để điều khiển; Port-mapped I/O dùng không gian địa chỉ riêng biệt và các lệnh chuyên dụng (như IN/OUT)</v>
+        <v>Memory-mapped I/O chỉ được áp dụng trên các dòng vi điều khiển 8-bit Intel 8051</v>
       </c>
       <c r="F23" t="str">
         <v>Port-mapped I/O cho phép CPU truy cập ngoại vi nhanh hơn gấp nhiều lần so với Memory-mapped I/O</v>
       </c>
       <c r="G23" t="str">
-        <v>Memory-mapped I/O chỉ được áp dụng trên các dòng vi điều khiển 8-bit Intel 8051</v>
+        <v>Memory-mapped I/O ánh xạ thanh ghi ngoại vi vào không gian địa chỉ bộ nhớ chung, cho phép dùng mọi lệnh truy cập bộ nhớ để điều khiển; Port-mapped I/O dùng không gian địa chỉ riêng biệt và các lệnh chuyên dụng (như IN/OUT)</v>
       </c>
       <c r="H23" t="str">
         <v>Port-mapped I/O bắt buộc phải sử dụng các con trỏ hàm trong ngôn ngữ C để điều khiển thanh ghi</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1091,10 +1091,10 @@
         <v>Trùng địa chỉ tĩnh trên cùng một bus vật lý sẽ gây xung đột dữ liệu (cả hai cùng phản hồi ACK/Data). Mux I2C (như TCA9548A) cho phép CPU chọn nhánh giao tiếp hoạt động độc lập, hoặc Bit-banging để tạo cổng I2C ảo.</v>
       </c>
       <c r="E24" t="str">
+        <v>Thay đổi địa chỉ của một trong hai cảm biến bằng cách viết lệnh ghi đè vào bộ nhớ ROM của nó</v>
+      </c>
+      <c r="F24" t="str">
         <v>Sử dụng chip Mux I2C (I2C Multiplexer) để phân tách bus thành các nhánh độc lập, hoặc kết nối cảm biến vào các chân GPIO khác và giả lập I2C bằng phần mềm (Bit-banging)</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Thay đổi địa chỉ của một trong hai cảm biến bằng cách viết lệnh ghi đè vào bộ nhớ ROM của nó</v>
       </c>
       <c r="G24" t="str">
         <v>Mắc nối tiếp hai cảm biến với nhau theo sơ đồ nối tiếp dạng Daisy Chain</v>
@@ -1103,7 +1103,7 @@
         <v>Nâng tần số hoạt động của SCL lên gấp đôi để hai cảm biến tự động đàm phán phân chia thời gian</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Đây là các tham số định thời phần cứng (AC characteristics). Nếu phần mềm cấu hình SPI chạy quá nhanh vượt quá giới hạn Set-up/Hold time của Slave, Slave sẽ nhận sai bit dữ liệu, gây lỗi truyền tin.</v>
       </c>
       <c r="E25" t="str">
+        <v>Set-up Time: Thời gian khởi động nguồn cấp ngoại vi; Hold Time: Thời gian chờ ngoại vi phản hồi lệnh</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Hai tham số này chỉ liên quan đến thiết kế mạch in (PCB layout) và không ảnh hưởng đến phần mềm cấu hình SPI</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Set-up Time: Thời gian cần thiết để Master kéo chân CS xuống thấp; Hold Time: Thời gian giữ chân CS ở mức thấp</v>
+      </c>
+      <c r="H25" t="str">
         <v>Set-up Time: Thời gian tối thiểu dữ liệu trên đường MISO/MOSI phải ổn định TRƯỚC sườn xung lấy mẫu; Hold Time: Thời gian tối thiểu dữ liệu phải giữ nguyên SAU sườn xung đó</v>
       </c>
-      <c r="F25" t="str">
-        <v>Set-up Time: Thời gian cần thiết để Master kéo chân CS xuống thấp; Hold Time: Thời gian giữ chân CS ở mức thấp</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Set-up Time: Thời gian khởi động nguồn cấp ngoại vi; Hold Time: Thời gian chờ ngoại vi phản hồi lệnh</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Hai tham số này chỉ liên quan đến thiết kế mạch in (PCB layout) và không ảnh hưởng đến phần mềm cấu hình SPI</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>ECC RAM/Flash bảo vệ tính toàn vẹn hệ thống (functional safety, tiêu chuẩn ISO 26262). Nó tự động phát hiện và sửa các lỗi 1-bit (Single Error Correction) và phát hiện lỗi 2-bit (Double Error Detection) ở mức phần cứng.</v>
       </c>
       <c r="E26" t="str">
+        <v>Để cho phép vi điều khiển hoạt động được trong môi trường không có nguồn điện cấp</v>
+      </c>
+      <c r="F26" t="str">
         <v>Để phát hiện và tự động sửa các lỗi đảo bit ngẫu nhiên (do nhiễu điện từ, tia vũ trụ hoặc lão hóa linh kiện) tránh việc CPU thực thi sai lệnh gây tai nạn</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>Để mã hóa dữ liệu tránh việc bị sao chép trộm mã nguồn từ chip ra bên ngoài</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>Để tự động tăng tốc độ xử lý các phép toán số thực của nhân CPU lên gấp đôi</v>
       </c>
-      <c r="H26" t="str">
-        <v>Để cho phép vi điều khiển hoạt động được trong môi trường không có nguồn điện cấp</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
